--- a/Old_Design/docs/Test_Rig_Sensors.xlsx
+++ b/Old_Design/docs/Test_Rig_Sensors.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCP\Industrial-Test-Rig-Simulator\Industrial-Test-Rig-Simulator\Old Design\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Industrial-Test-Rig-Simulator\Old_Design\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C533333-B521-45B5-AE09-3FE5E8BFA8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E59D23-49FC-4B08-9469-CE70DE2002E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sensors" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>SCT-013-030</t>
   </si>
   <si>
-    <t>Sensor Name</t>
-  </si>
-  <si>
     <t>Acoustic</t>
   </si>
   <si>
@@ -69,15 +66,9 @@
     <t>And GATE</t>
   </si>
   <si>
-    <t>SN7404hcn</t>
-  </si>
-  <si>
     <t>Accelerometer</t>
   </si>
   <si>
-    <t>MPU9050</t>
-  </si>
-  <si>
     <t>Quantity Used</t>
   </si>
   <si>
@@ -133,6 +124,63 @@
   </si>
   <si>
     <t>Arduino Uno R3</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>MPU9250</t>
+  </si>
+  <si>
+    <t>Specification</t>
+  </si>
+  <si>
+    <t>3-axis accelerometer; ±2/±4/±8/±16 g; 16-bit resolution</t>
+  </si>
+  <si>
+    <t>Sound detection; adjustable sensitivity; digital comparator output</t>
+  </si>
+  <si>
+    <t>Float-based level detection; horizontal mounting; switch-type output</t>
+  </si>
+  <si>
+    <t>Float-based level detection; vertical mounting; switch-type output</t>
+  </si>
+  <si>
+    <t>8 analog inputs; 12-bit ADC; up to 10 kS/s</t>
+  </si>
+  <si>
+    <t>AC current transformer; 0–30 A AC; non-invasive measurement</t>
+  </si>
+  <si>
+    <t>Non-contact RPM measurement; rotational-speed monitoring; digital/analog output depending on configuration</t>
+  </si>
+  <si>
+    <t>−40 to +80 °C; 0–100% RH; digital output</t>
+  </si>
+  <si>
+    <t>Incremental rotary encoder; 2000 PPR; 5–24 VDC</t>
+  </si>
+  <si>
+    <t>Multiple DC rails; +12 V, +5 V and +3.3 V outputs; AC input</t>
+  </si>
+  <si>
+    <t>AC motor driven; liquid pumping; flow/pressure dependent on model</t>
+  </si>
+  <si>
+    <t>Hex inverter; 6 NOT gates; TTL logic</t>
+  </si>
+  <si>
+    <t>Electromechanical relay; typically 5 V control; load switching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SN7404HCN</t>
+  </si>
+  <si>
+    <t>ATmega328P microcontroller; 16 MHz clock speed; 14 digital I/O, 6 analog inputs</t>
   </si>
 </sst>
 </file>
@@ -197,19 +245,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -224,7 +260,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,278 +554,287 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91456F87-2E09-44D1-A19F-87D1E8730BED}">
-  <dimension ref="A2:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:E18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="D8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="D4" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="B16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="D5" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="9">
+      <c r="C18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>9</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>13</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>14</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>15</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
